--- a/module_1-from_ai_model_to_ai_product/assignment_2-RAG/assignment2_improvement_cycles.xlsx
+++ b/module_1-from_ai_model_to_ai_product/assignment_2-RAG/assignment2_improvement_cycles.xlsx
@@ -471,13 +471,13 @@
         <v>0.4233333333333333</v>
       </c>
       <c r="E2" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="F2" t="n">
-        <v>0.34</v>
+        <v>0.33</v>
       </c>
       <c r="G2" t="n">
-        <v>0.43</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="3">
@@ -498,7 +498,7 @@
         <v>0.2883333333333333</v>
       </c>
       <c r="E3" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="F3" t="n">
         <v>0.22</v>
@@ -525,13 +525,13 @@
         <v>0.7123809523809523</v>
       </c>
       <c r="E4" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="F4" t="n">
-        <v>0.34</v>
+        <v>0.33</v>
       </c>
       <c r="G4" t="n">
-        <v>0.43</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="5">
@@ -552,13 +552,13 @@
         <v>0.31875</v>
       </c>
       <c r="E5" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="F5" t="n">
-        <v>0.31</v>
+        <v>0.3</v>
       </c>
       <c r="G5" t="n">
-        <v>0.37</v>
+        <v>0.36</v>
       </c>
     </row>
   </sheetData>
